--- a/conformance/cases/xlsx-09-absolute-target.xlsx
+++ b/conformance/cases/xlsx-09-absolute-target.xlsx
@@ -89,7 +89,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bắt đầu</t>
+          <t xml:space="preserve">Start</t>
         </is>
       </c>
     </row>
@@ -106,7 +106,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">gửi yêu cầu</t>
+          <t xml:space="preserve">send request</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -133,7 +133,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xử lý</t>
+          <t xml:space="preserve">Process</t>
         </is>
       </c>
     </row>
@@ -172,7 +172,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xong</t>
+          <t xml:space="preserve">Done</t>
         </is>
       </c>
     </row>
